--- a/tests/fixtures/17_excel_template_invoice/17_excel_template_invoice_pattern-from-claude.xlsx
+++ b/tests/fixtures/17_excel_template_invoice/17_excel_template_invoice_pattern-from-claude.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -809,152 +809,158 @@
       <c r="F15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>invoice.billto</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>START:</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>table:*</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n"/>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>HEADER:1</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>invoice_header</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>DATA:*</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>company.info</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>table:*</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n"/>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>HEADER:1</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>bill_to_label</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>invoice_num_label</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>date_label</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>terms_label</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="n"/>
-      <c r="B22" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>DATA:*</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>invoice.billto</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>invoice.number</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>invoice.date</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>invoice.terms</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>cell:next</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>contact_intro</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -964,7 +970,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>IGNORE</t>
+          <t>contact_intro</t>
         </is>
       </c>
       <c r="C24" s="6" t="n"/>
@@ -980,7 +986,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="C25" s="6" t="n"/>
@@ -996,7 +1002,7 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>contact.note</t>
+          <t>contact_details</t>
         </is>
       </c>
       <c r="C26" s="6" t="n"/>
@@ -1005,16 +1011,32 @@
       <c r="F26" s="6" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>contact.note</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>END:</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tests/fixtures/17_excel_template_invoice/17_excel_template_invoice_pattern-from-claude.xlsx
+++ b/tests/fixtures/17_excel_template_invoice/17_excel_template_invoice_pattern-from-claude.xlsx
@@ -662,7 +662,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>If you have any questions about this invoice, please contact</t>
+          <t>First Up Consultants</t>
         </is>
       </c>
       <c r="E9" s="2" t="n"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Cora Thomas at (516) 555-0135 or cora@example.com.</t>
+          <t>INVOICE</t>
         </is>
       </c>
       <c r="E10" s="2" t="n"/>
